--- a/2 - DATA/Data.xlsx
+++ b/2 - DATA/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="FIXES" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,12 @@
     <sheet name="PERIODE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CATEGORIE_CATALOGUE" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CATEGORIE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CATEGORIE_TARGET" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">CATEGORIE_TARGET!$A$1:$D$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">CATEGORIE_TARGET!$A$1:$D$113</definedName>
+  </definedNames>
   <calcPr/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
@@ -20,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>ID_FIXES</t>
   </si>
@@ -379,6 +384,9 @@
     <t>BoursoBank</t>
   </si>
   <si>
+    <t xml:space="preserve">Trade Republic</t>
+  </si>
+  <si>
     <t>Impôts</t>
   </si>
   <si>
@@ -404,12 +412,18 @@
   </si>
   <si>
     <t>COPIE</t>
+  </si>
+  <si>
+    <t>OBJECTIF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-40C]"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11.000000"/>
@@ -668,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="42">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -679,7 +693,6 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -712,6 +725,7 @@
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -737,6 +751,24 @@
     </xf>
     <xf fontId="0" fillId="4" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="2" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1280,7 +1312,7 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1409,31 +1441,31 @@
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>1</v>
       </c>
       <c r="C2" s="3">
         <f t="shared" ref="C2:C9" si="0">IF(B2=0,C1,B2)</f>
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E2">
@@ -1442,13 +1474,13 @@
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E3">
@@ -1457,13 +1489,13 @@
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E4">
@@ -1472,13 +1504,13 @@
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E5">
@@ -1487,13 +1519,13 @@
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E6">
@@ -1502,13 +1534,13 @@
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="E7">
@@ -1517,13 +1549,13 @@
       </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E8">
@@ -1532,13 +1564,13 @@
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E9">
@@ -1547,13 +1579,13 @@
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="3">
         <f>IF(B10=0,C9,B10)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E10">
@@ -1562,13 +1594,13 @@
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="3">
         <f t="shared" ref="C11:C74" si="1">IF(B11=0,C10,B11)</f>
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E11">
@@ -1577,13 +1609,13 @@
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E12">
@@ -1592,13 +1624,13 @@
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="11"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E13">
@@ -1607,13 +1639,13 @@
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E14">
@@ -1622,13 +1654,13 @@
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E15">
@@ -1637,13 +1669,13 @@
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E16">
@@ -1652,13 +1684,13 @@
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E17">
@@ -1667,13 +1699,13 @@
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
       <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>36</v>
       </c>
       <c r="E18">
@@ -1682,17 +1714,17 @@
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="8">
         <v>2</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E19">
@@ -1701,13 +1733,13 @@
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E20">
@@ -1716,13 +1748,13 @@
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>40</v>
       </c>
       <c r="E21">
@@ -1731,13 +1763,13 @@
       </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E22">
@@ -1746,13 +1778,13 @@
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E23">
@@ -1761,13 +1793,13 @@
       </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="11"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E24">
@@ -1776,13 +1808,13 @@
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E25">
@@ -1791,13 +1823,13 @@
       </c>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
       <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="9" t="s">
         <v>45</v>
       </c>
       <c r="E26">
@@ -1806,17 +1838,17 @@
       </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="8">
         <v>3</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>47</v>
       </c>
       <c r="E27">
@@ -1825,13 +1857,13 @@
       </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E28">
@@ -1840,13 +1872,13 @@
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>49</v>
       </c>
       <c r="E29">
@@ -1855,13 +1887,13 @@
       </c>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E30">
@@ -1870,13 +1902,13 @@
       </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="9" t="s">
         <v>51</v>
       </c>
       <c r="E31">
@@ -1885,13 +1917,13 @@
       </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
         <v>52</v>
       </c>
       <c r="E32">
@@ -1900,13 +1932,13 @@
       </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
       <c r="C33" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E33">
@@ -1915,17 +1947,17 @@
       </c>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="8">
         <v>4</v>
       </c>
       <c r="C34" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E34">
@@ -1934,13 +1966,13 @@
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="11"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="9" t="s">
         <v>56</v>
       </c>
       <c r="E35">
@@ -1949,13 +1981,13 @@
       </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="11"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E36">
@@ -1964,13 +1996,13 @@
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="11"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="14" t="s">
         <v>58</v>
       </c>
       <c r="E37">
@@ -1979,13 +2011,13 @@
       </c>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="11"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="10"/>
       <c r="C38" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E38">
@@ -1994,13 +2026,13 @@
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="11"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="9" t="s">
         <v>60</v>
       </c>
       <c r="E39">
@@ -2009,13 +2041,13 @@
       </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="10"/>
       <c r="C40" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="9" t="s">
         <v>61</v>
       </c>
       <c r="E40">
@@ -2024,13 +2056,13 @@
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="11"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="10"/>
       <c r="C41" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="9" t="s">
         <v>62</v>
       </c>
       <c r="E41">
@@ -2039,13 +2071,13 @@
       </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="11"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="10"/>
       <c r="C42" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E42">
@@ -2054,13 +2086,13 @@
       </c>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="11"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="9" t="s">
         <v>64</v>
       </c>
       <c r="E43">
@@ -2069,13 +2101,13 @@
       </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
       <c r="C44" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="E44">
@@ -2084,17 +2116,17 @@
       </c>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="8">
         <v>5</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E45">
@@ -2103,13 +2135,13 @@
       </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="9" t="s">
         <v>68</v>
       </c>
       <c r="E46">
@@ -2118,13 +2150,13 @@
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="16"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="9" t="s">
         <v>69</v>
       </c>
       <c r="E47">
@@ -2133,13 +2165,13 @@
       </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="16"/>
-      <c r="B48" s="13"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="12"/>
       <c r="C48" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E48">
@@ -2148,17 +2180,17 @@
       </c>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="8">
         <v>6</v>
       </c>
       <c r="C49" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="9" t="s">
         <v>72</v>
       </c>
       <c r="E49">
@@ -2167,13 +2199,13 @@
       </c>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="11"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="10"/>
       <c r="C50" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="E50">
@@ -2182,13 +2214,13 @@
       </c>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="11"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="10"/>
       <c r="C51" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="9" t="s">
         <v>74</v>
       </c>
       <c r="E51">
@@ -2197,13 +2229,13 @@
       </c>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="11"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="10"/>
       <c r="C52" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="9" t="s">
         <v>75</v>
       </c>
       <c r="E52">
@@ -2212,13 +2244,13 @@
       </c>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="11"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="10"/>
       <c r="C53" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="9" t="s">
         <v>76</v>
       </c>
       <c r="E53">
@@ -2227,13 +2259,13 @@
       </c>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="10"/>
       <c r="C54" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E54">
@@ -2242,13 +2274,13 @@
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="11"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="10"/>
       <c r="C55" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E55">
@@ -2257,13 +2289,13 @@
       </c>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="11"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="9" t="s">
         <v>79</v>
       </c>
       <c r="E56">
@@ -2272,13 +2304,13 @@
       </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="11"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="10"/>
       <c r="C57" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="9" t="s">
         <v>80</v>
       </c>
       <c r="E57">
@@ -2287,13 +2319,13 @@
       </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="8"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="10"/>
       <c r="C58" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="9" t="s">
         <v>81</v>
       </c>
       <c r="E58">
@@ -2302,13 +2334,13 @@
       </c>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="8"/>
-      <c r="B59" s="11"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="10"/>
       <c r="C59" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="9" t="s">
         <v>82</v>
       </c>
       <c r="E59">
@@ -2317,13 +2349,13 @@
       </c>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="11"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="10"/>
       <c r="C60" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="9" t="s">
         <v>83</v>
       </c>
       <c r="E60">
@@ -2332,13 +2364,13 @@
       </c>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
       <c r="C61" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
         <v>84</v>
       </c>
       <c r="E61">
@@ -2347,17 +2379,17 @@
       </c>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="8">
         <v>7</v>
       </c>
       <c r="C62" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="9" t="s">
         <v>86</v>
       </c>
       <c r="E62">
@@ -2366,13 +2398,13 @@
       </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="16"/>
-      <c r="B63" s="11"/>
+      <c r="A63" s="15"/>
+      <c r="B63" s="10"/>
       <c r="C63" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="9" t="s">
         <v>87</v>
       </c>
       <c r="E63">
@@ -2381,13 +2413,13 @@
       </c>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="16"/>
-      <c r="B64" s="11"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="10"/>
       <c r="C64" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="9" t="s">
         <v>88</v>
       </c>
       <c r="E64">
@@ -2396,13 +2428,13 @@
       </c>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="16"/>
-      <c r="B65" s="11"/>
+      <c r="A65" s="15"/>
+      <c r="B65" s="10"/>
       <c r="C65" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="9" t="s">
         <v>89</v>
       </c>
       <c r="E65">
@@ -2411,13 +2443,13 @@
       </c>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="16"/>
-      <c r="B66" s="11"/>
+      <c r="A66" s="15"/>
+      <c r="B66" s="10"/>
       <c r="C66" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E66">
@@ -2426,13 +2458,13 @@
       </c>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="16"/>
-      <c r="B67" s="13"/>
+      <c r="A67" s="15"/>
+      <c r="B67" s="12"/>
       <c r="C67" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="14" t="s">
         <v>91</v>
       </c>
       <c r="E67">
@@ -2441,17 +2473,17 @@
       </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="8">
         <v>8</v>
       </c>
       <c r="C68" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="14" t="s">
         <v>93</v>
       </c>
       <c r="E68">
@@ -2460,13 +2492,13 @@
       </c>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="16"/>
-      <c r="B69" s="11"/>
+      <c r="A69" s="15"/>
+      <c r="B69" s="10"/>
       <c r="C69" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" s="14" t="s">
         <v>94</v>
       </c>
       <c r="E69">
@@ -2475,13 +2507,13 @@
       </c>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="16"/>
-      <c r="B70" s="13"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="12"/>
       <c r="C70" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="14" t="s">
         <v>95</v>
       </c>
       <c r="E70">
@@ -2490,17 +2522,17 @@
       </c>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="8">
         <v>9</v>
       </c>
       <c r="C71" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="9" t="s">
         <v>97</v>
       </c>
       <c r="E71">
@@ -2509,13 +2541,13 @@
       </c>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="16"/>
-      <c r="B72" s="11"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="10"/>
       <c r="C72" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="9" t="s">
         <v>98</v>
       </c>
       <c r="E72">
@@ -2524,13 +2556,13 @@
       </c>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="16"/>
-      <c r="B73" s="11"/>
+      <c r="A73" s="15"/>
+      <c r="B73" s="10"/>
       <c r="C73" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E73">
@@ -2539,13 +2571,13 @@
       </c>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="16"/>
-      <c r="B74" s="11"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="10"/>
       <c r="C74" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E74">
@@ -2554,13 +2586,13 @@
       </c>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="16"/>
-      <c r="B75" s="11"/>
+      <c r="A75" s="15"/>
+      <c r="B75" s="10"/>
       <c r="C75" s="3">
-        <f t="shared" ref="C75:C97" si="2">IF(B75=0,C74,B75)</f>
+        <f t="shared" ref="C75:C98" si="2">IF(B75=0,C74,B75)</f>
         <v>9</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E75">
@@ -2569,13 +2601,13 @@
       </c>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="16"/>
-      <c r="B76" s="11"/>
+      <c r="A76" s="15"/>
+      <c r="B76" s="10"/>
       <c r="C76" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="9" t="s">
         <v>101</v>
       </c>
       <c r="E76">
@@ -2584,13 +2616,13 @@
       </c>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="16"/>
-      <c r="B77" s="11"/>
+      <c r="A77" s="15"/>
+      <c r="B77" s="10"/>
       <c r="C77" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="9" t="s">
         <v>25</v>
       </c>
       <c r="E77">
@@ -2599,13 +2631,13 @@
       </c>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="16"/>
-      <c r="B78" s="11"/>
+      <c r="A78" s="15"/>
+      <c r="B78" s="10"/>
       <c r="C78" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" s="9" t="s">
         <v>102</v>
       </c>
       <c r="E78">
@@ -2614,13 +2646,13 @@
       </c>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="16"/>
-      <c r="B79" s="13"/>
+      <c r="A79" s="15"/>
+      <c r="B79" s="12"/>
       <c r="C79" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="9" t="s">
         <v>103</v>
       </c>
       <c r="E79">
@@ -2629,17 +2661,17 @@
       </c>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="8">
         <v>10</v>
       </c>
       <c r="C80" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="9" t="s">
         <v>105</v>
       </c>
       <c r="E80">
@@ -2648,13 +2680,13 @@
       </c>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="16"/>
-      <c r="B81" s="11"/>
+      <c r="A81" s="15"/>
+      <c r="B81" s="10"/>
       <c r="C81" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="9" t="s">
         <v>106</v>
       </c>
       <c r="E81">
@@ -2663,13 +2695,13 @@
       </c>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="16"/>
-      <c r="B82" s="13"/>
+      <c r="A82" s="15"/>
+      <c r="B82" s="12"/>
       <c r="C82" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E82">
@@ -2678,17 +2710,17 @@
       </c>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="8">
         <v>11</v>
       </c>
       <c r="C83" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="9" t="s">
         <v>109</v>
       </c>
       <c r="E83">
@@ -2697,13 +2729,13 @@
       </c>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="8"/>
-      <c r="B84" s="11"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="10"/>
       <c r="C84" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E84">
@@ -2712,13 +2744,13 @@
       </c>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="8"/>
-      <c r="B85" s="11"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="10"/>
       <c r="C85" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E85">
@@ -2727,13 +2759,13 @@
       </c>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="12"/>
-      <c r="B86" s="13"/>
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
       <c r="C86" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="9" t="s">
         <v>112</v>
       </c>
       <c r="E86">
@@ -2742,17 +2774,17 @@
       </c>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="8">
         <v>12</v>
       </c>
       <c r="C87" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="9" t="s">
         <v>114</v>
       </c>
       <c r="E87">
@@ -2761,13 +2793,13 @@
       </c>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="8"/>
-      <c r="B88" s="11"/>
+      <c r="A88" s="7"/>
+      <c r="B88" s="10"/>
       <c r="C88" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" s="9" t="s">
         <v>115</v>
       </c>
       <c r="E88">
@@ -2776,13 +2808,13 @@
       </c>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="8"/>
-      <c r="B89" s="11"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="10"/>
       <c r="C89" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" s="9" t="s">
         <v>116</v>
       </c>
       <c r="E89">
@@ -2791,13 +2823,13 @@
       </c>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="8"/>
-      <c r="B90" s="11"/>
+      <c r="A90" s="7"/>
+      <c r="B90" s="10"/>
       <c r="C90" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="9" t="s">
         <v>117</v>
       </c>
       <c r="E90">
@@ -2806,13 +2838,13 @@
       </c>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="12"/>
-      <c r="B91" s="13"/>
+      <c r="A91" s="7"/>
+      <c r="B91" s="10"/>
       <c r="C91" s="3">
-        <f t="shared" si="2"/>
+        <f>IF(B91=0,C89,B91)</f>
         <v>12</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="9" t="s">
         <v>118</v>
       </c>
       <c r="E91">
@@ -2821,112 +2853,127 @@
       </c>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="3">
+        <f>IF(B92=0,C90,B92)</f>
+        <v>12</v>
+      </c>
+      <c r="D92" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B92" s="3">
+      <c r="E92">
+        <f>VLOOKUP(C92&amp;"_"&amp;D92,CATEGORIE!D:E,2,0)</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" ht="14.25">
+      <c r="A93" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B93" s="3">
         <v>13</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C93" s="3">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="D92" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E92">
-        <f>VLOOKUP(C92&amp;"_"&amp;D92,CATEGORIE!D:E,2,0)</f>
+      <c r="D93" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93">
+        <f>VLOOKUP(C93&amp;"_"&amp;D93,CATEGORIE!D:E,2,0)</f>
         <v>107</v>
       </c>
     </row>
-    <row r="93" ht="14.25">
-      <c r="A93" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B93" s="3">
+    <row r="94" ht="14.25">
+      <c r="A94" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B94" s="3">
         <v>14</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C94" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="D93" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E93">
-        <f>VLOOKUP(C93&amp;"_"&amp;D93,CATEGORIE!D:E,2,0)</f>
+      <c r="D94" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E94">
+        <f>VLOOKUP(C94&amp;"_"&amp;D94,CATEGORIE!D:E,2,0)</f>
         <v>108</v>
       </c>
     </row>
-    <row r="94" ht="14.25">
-      <c r="A94" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="B94" s="3">
+    <row r="95" ht="14.25">
+      <c r="A95" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" s="3">
         <v>15</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C95" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="D94" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E94">
-        <f>VLOOKUP(C94&amp;"_"&amp;D94,CATEGORIE!D:E,2,0)</f>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="95" ht="14.25">
-      <c r="A95" s="9" t="s">
+      <c r="D95" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="B95" s="9">
-        <v>16</v>
-      </c>
-      <c r="C95" s="3">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="E95">
         <f>VLOOKUP(C95&amp;"_"&amp;D95,CATEGORIE!D:E,2,0)</f>
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
+      <c r="A96" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="8">
+        <v>16</v>
+      </c>
       <c r="C96" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E96">
         <f>VLOOKUP(C96&amp;"_"&amp;D96,CATEGORIE!D:E,2,0)</f>
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="13"/>
-      <c r="B97" s="13"/>
+      <c r="A97" s="10"/>
+      <c r="B97" s="10"/>
       <c r="C97" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E97">
         <f>VLOOKUP(C97&amp;"_"&amp;D97,CATEGORIE!D:E,2,0)</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25">
+      <c r="A98" s="12"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E98">
+        <f>VLOOKUP(C98&amp;"_"&amp;D98,CATEGORIE!D:E,2,0)</f>
         <v>112</v>
       </c>
     </row>
-    <row r="98" ht="14.25"/>
+    <row r="99" ht="14.25"/>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="A2:A18"/>
@@ -2951,10 +2998,10 @@
     <mergeCell ref="B80:B82"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="B83:B86"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2974,19 +3021,19 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -3199,7 +3246,7 @@
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="5"/>
@@ -3216,7 +3263,7 @@
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="5"/>
@@ -3233,7 +3280,7 @@
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="5"/>
@@ -3250,7 +3297,7 @@
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="5"/>
@@ -4979,7 +5026,7 @@
         <v>13</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D108" t="str">
         <f t="shared" si="9"/>
@@ -4998,7 +5045,7 @@
         <v>14</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D109" t="str">
         <f t="shared" si="9"/>
@@ -5017,7 +5064,7 @@
         <v>15</v>
       </c>
       <c r="C110" s="28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D110" t="str">
         <f t="shared" si="9"/>
@@ -5036,7 +5083,7 @@
         <v>16</v>
       </c>
       <c r="C111" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D111" t="str">
         <f t="shared" si="9"/>
@@ -5073,7 +5120,7 @@
       <c r="B113" s="24">
         <v>16</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C113" s="30" t="s">
         <v>106</v>
       </c>
       <c r="D113" t="str">
@@ -5083,6 +5130,25 @@
       <c r="E113">
         <f t="shared" si="10"/>
         <v>112</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25">
+      <c r="A114" s="24">
+        <v>113</v>
+      </c>
+      <c r="B114" s="24">
+        <v>12</v>
+      </c>
+      <c r="C114" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D114" t="str">
+        <f>B114&amp;"_"&amp;C114</f>
+        <v xml:space="preserve">12_Trade Republic</v>
+      </c>
+      <c r="E114">
+        <f>A114</f>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -5091,4 +5157,1370 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="2" width="17.140625"/>
+    <col customWidth="1" min="3" max="3" width="23.7109375"/>
+    <col customWidth="1" min="4" max="4" style="32" width="23.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="19">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="35"/>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="35"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="35"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="35"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="35"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="19">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="35"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="19">
+        <v>8</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="35"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="35"/>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="35"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="35"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="19">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="35"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="35"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="35"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="35"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="19">
+        <v>16</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="35"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="22">
+        <v>17</v>
+      </c>
+      <c r="B18" s="22">
+        <v>1</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="36"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="22">
+        <v>18</v>
+      </c>
+      <c r="B19" s="22">
+        <v>1</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="36"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="22">
+        <v>19</v>
+      </c>
+      <c r="B20" s="22">
+        <v>1</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="36"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="22">
+        <v>20</v>
+      </c>
+      <c r="B21" s="22">
+        <v>1</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="36"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="36"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="22">
+        <v>22</v>
+      </c>
+      <c r="B23" s="22">
+        <v>1</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="36"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="22">
+        <v>23</v>
+      </c>
+      <c r="B24" s="22">
+        <v>1</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="36"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="22">
+        <v>24</v>
+      </c>
+      <c r="B25" s="22">
+        <v>1</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="36"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="22">
+        <v>25</v>
+      </c>
+      <c r="B26" s="22">
+        <v>1</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="36"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="22">
+        <v>26</v>
+      </c>
+      <c r="B27" s="22">
+        <v>1</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="36"/>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="22">
+        <v>27</v>
+      </c>
+      <c r="B28" s="22">
+        <v>1</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="36"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="22">
+        <v>28</v>
+      </c>
+      <c r="B29" s="22">
+        <v>1</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="36"/>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="22">
+        <v>29</v>
+      </c>
+      <c r="B30" s="22">
+        <v>1</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="36"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="22">
+        <v>30</v>
+      </c>
+      <c r="B31" s="22">
+        <v>1</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="36"/>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="22">
+        <v>31</v>
+      </c>
+      <c r="B32" s="22">
+        <v>1</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="36"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="22">
+        <v>32</v>
+      </c>
+      <c r="B33" s="22">
+        <v>1</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="36"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="22">
+        <v>33</v>
+      </c>
+      <c r="B34" s="22">
+        <v>1</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="36"/>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="24">
+        <v>34</v>
+      </c>
+      <c r="B35" s="24">
+        <v>2</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="37"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="24">
+        <v>35</v>
+      </c>
+      <c r="B36" s="24">
+        <v>2</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="37"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="24">
+        <v>36</v>
+      </c>
+      <c r="B37" s="24">
+        <v>2</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="37"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="24">
+        <v>37</v>
+      </c>
+      <c r="B38" s="24">
+        <v>2</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="37"/>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="24">
+        <v>38</v>
+      </c>
+      <c r="B39" s="24">
+        <v>2</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="37"/>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="24">
+        <v>39</v>
+      </c>
+      <c r="B40" s="24">
+        <v>2</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="37"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="24">
+        <v>40</v>
+      </c>
+      <c r="B41" s="24">
+        <v>2</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="37"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="24">
+        <v>41</v>
+      </c>
+      <c r="B42" s="24">
+        <v>2</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="37"/>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="22">
+        <v>42</v>
+      </c>
+      <c r="B43" s="22">
+        <v>3</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="36"/>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" s="22">
+        <v>43</v>
+      </c>
+      <c r="B44" s="22">
+        <v>3</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="36"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="22">
+        <v>44</v>
+      </c>
+      <c r="B45" s="22">
+        <v>3</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="36"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="22">
+        <v>45</v>
+      </c>
+      <c r="B46" s="22">
+        <v>3</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="36"/>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="22">
+        <v>46</v>
+      </c>
+      <c r="B47" s="22">
+        <v>3</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="36"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="22">
+        <v>47</v>
+      </c>
+      <c r="B48" s="22">
+        <v>3</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="36"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="22">
+        <v>48</v>
+      </c>
+      <c r="B49" s="22">
+        <v>3</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="36"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="24">
+        <v>49</v>
+      </c>
+      <c r="B50" s="24">
+        <v>4</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="37"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="24">
+        <v>50</v>
+      </c>
+      <c r="B51" s="24">
+        <v>4</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="37"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="24">
+        <v>51</v>
+      </c>
+      <c r="B52" s="24">
+        <v>4</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="37"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="24">
+        <v>52</v>
+      </c>
+      <c r="B53" s="24">
+        <v>4</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53" s="38"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54" s="24">
+        <v>53</v>
+      </c>
+      <c r="B54" s="24">
+        <v>4</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="37"/>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="24">
+        <v>54</v>
+      </c>
+      <c r="B55" s="24">
+        <v>4</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="37"/>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="24">
+        <v>55</v>
+      </c>
+      <c r="B56" s="24">
+        <v>4</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="37"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="24">
+        <v>56</v>
+      </c>
+      <c r="B57" s="24">
+        <v>4</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="37"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="24">
+        <v>57</v>
+      </c>
+      <c r="B58" s="24">
+        <v>4</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="37"/>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="24">
+        <v>58</v>
+      </c>
+      <c r="B59" s="24">
+        <v>4</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" s="37"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="24">
+        <v>59</v>
+      </c>
+      <c r="B60" s="24">
+        <v>4</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" s="37"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="22">
+        <v>60</v>
+      </c>
+      <c r="B61" s="22">
+        <v>5</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="22">
+        <v>61</v>
+      </c>
+      <c r="B62" s="22">
+        <v>5</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" s="36"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="22">
+        <v>62</v>
+      </c>
+      <c r="B63" s="22">
+        <v>5</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="36"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="22">
+        <v>63</v>
+      </c>
+      <c r="B64" s="22">
+        <v>5</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="36"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="24">
+        <v>64</v>
+      </c>
+      <c r="B65" s="24">
+        <v>6</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="37">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="24">
+        <v>65</v>
+      </c>
+      <c r="B66" s="24">
+        <v>6</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="37"/>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="24">
+        <v>66</v>
+      </c>
+      <c r="B67" s="24">
+        <v>6</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="37">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="24">
+        <v>67</v>
+      </c>
+      <c r="B68" s="24">
+        <v>6</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="37"/>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="24">
+        <v>68</v>
+      </c>
+      <c r="B69" s="24">
+        <v>6</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="37"/>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="24">
+        <v>69</v>
+      </c>
+      <c r="B70" s="24">
+        <v>6</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="37">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71" s="24">
+        <v>70</v>
+      </c>
+      <c r="B71" s="24">
+        <v>6</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="37"/>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="A72" s="24">
+        <v>71</v>
+      </c>
+      <c r="B72" s="24">
+        <v>6</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="37"/>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="A73" s="24">
+        <v>72</v>
+      </c>
+      <c r="B73" s="24">
+        <v>6</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" s="37"/>
+    </row>
+    <row r="74" ht="14.25">
+      <c r="A74" s="24">
+        <v>73</v>
+      </c>
+      <c r="B74" s="24">
+        <v>6</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D74" s="37"/>
+    </row>
+    <row r="75" ht="14.25">
+      <c r="A75" s="24">
+        <v>74</v>
+      </c>
+      <c r="B75" s="24">
+        <v>6</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="37"/>
+    </row>
+    <row r="76" ht="14.25">
+      <c r="A76" s="24">
+        <v>75</v>
+      </c>
+      <c r="B76" s="24">
+        <v>6</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" s="37"/>
+    </row>
+    <row r="77" ht="14.25">
+      <c r="A77" s="24">
+        <v>76</v>
+      </c>
+      <c r="B77" s="24">
+        <v>6</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D77" s="37"/>
+    </row>
+    <row r="78" ht="14.25">
+      <c r="A78" s="22">
+        <v>77</v>
+      </c>
+      <c r="B78" s="22">
+        <v>7</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" s="36">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="79" ht="14.25">
+      <c r="A79" s="22">
+        <v>78</v>
+      </c>
+      <c r="B79" s="22">
+        <v>7</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="36"/>
+    </row>
+    <row r="80" ht="14.25">
+      <c r="A80" s="22">
+        <v>79</v>
+      </c>
+      <c r="B80" s="22">
+        <v>7</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="36"/>
+    </row>
+    <row r="81" ht="14.25">
+      <c r="A81" s="22">
+        <v>80</v>
+      </c>
+      <c r="B81" s="22">
+        <v>7</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="36"/>
+    </row>
+    <row r="82" ht="14.25">
+      <c r="A82" s="22">
+        <v>81</v>
+      </c>
+      <c r="B82" s="22">
+        <v>7</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="36"/>
+    </row>
+    <row r="83" ht="14.25">
+      <c r="A83" s="22">
+        <v>82</v>
+      </c>
+      <c r="B83" s="22">
+        <v>7</v>
+      </c>
+      <c r="C83" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D83" s="39"/>
+    </row>
+    <row r="84" ht="14.25">
+      <c r="A84" s="24">
+        <v>83</v>
+      </c>
+      <c r="B84" s="24">
+        <v>8</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D84" s="38"/>
+    </row>
+    <row r="85" ht="14.25">
+      <c r="A85" s="24">
+        <v>84</v>
+      </c>
+      <c r="B85" s="24">
+        <v>8</v>
+      </c>
+      <c r="C85" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" s="38"/>
+    </row>
+    <row r="86" ht="14.25">
+      <c r="A86" s="24">
+        <v>85</v>
+      </c>
+      <c r="B86" s="24">
+        <v>8</v>
+      </c>
+      <c r="C86" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D86" s="38"/>
+    </row>
+    <row r="87" ht="14.25">
+      <c r="A87" s="24">
+        <v>86</v>
+      </c>
+      <c r="B87" s="24">
+        <v>9</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" s="37"/>
+    </row>
+    <row r="88" ht="14.25">
+      <c r="A88" s="22">
+        <v>87</v>
+      </c>
+      <c r="B88" s="22">
+        <v>9</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" s="36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" ht="14.25">
+      <c r="A89" s="22">
+        <v>88</v>
+      </c>
+      <c r="B89" s="22">
+        <v>9</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" s="36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25">
+      <c r="A90" s="22">
+        <v>89</v>
+      </c>
+      <c r="B90" s="22">
+        <v>9</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90" s="36"/>
+    </row>
+    <row r="91" ht="14.25">
+      <c r="A91" s="22">
+        <v>90</v>
+      </c>
+      <c r="B91" s="22">
+        <v>9</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="36"/>
+    </row>
+    <row r="92" ht="14.25">
+      <c r="A92" s="22">
+        <v>91</v>
+      </c>
+      <c r="B92" s="22">
+        <v>9</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" s="36"/>
+    </row>
+    <row r="93" ht="14.25">
+      <c r="A93" s="22">
+        <v>92</v>
+      </c>
+      <c r="B93" s="22">
+        <v>9</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D93" s="36"/>
+    </row>
+    <row r="94" ht="14.25">
+      <c r="A94" s="22">
+        <v>93</v>
+      </c>
+      <c r="B94" s="22">
+        <v>9</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D94" s="36"/>
+    </row>
+    <row r="95" ht="14.25">
+      <c r="A95" s="22">
+        <v>94</v>
+      </c>
+      <c r="B95" s="22">
+        <v>9</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D95" s="36"/>
+    </row>
+    <row r="96" ht="14.25">
+      <c r="A96" s="24">
+        <v>95</v>
+      </c>
+      <c r="B96" s="24">
+        <v>10</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" s="37"/>
+    </row>
+    <row r="97" ht="14.25">
+      <c r="A97" s="24">
+        <v>96</v>
+      </c>
+      <c r="B97" s="24">
+        <v>10</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" s="37"/>
+    </row>
+    <row r="98" ht="14.25">
+      <c r="A98" s="24">
+        <v>97</v>
+      </c>
+      <c r="B98" s="24">
+        <v>10</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98" s="37">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25">
+      <c r="A99" s="22">
+        <v>98</v>
+      </c>
+      <c r="B99" s="22">
+        <v>11</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D99" s="36"/>
+    </row>
+    <row r="100" ht="14.25">
+      <c r="A100" s="22">
+        <v>99</v>
+      </c>
+      <c r="B100" s="22">
+        <v>11</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D100" s="36"/>
+    </row>
+    <row r="101" ht="14.25">
+      <c r="A101" s="22">
+        <v>100</v>
+      </c>
+      <c r="B101" s="22">
+        <v>11</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D101" s="36"/>
+    </row>
+    <row r="102" ht="14.25">
+      <c r="A102" s="22">
+        <v>101</v>
+      </c>
+      <c r="B102" s="22">
+        <v>11</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102" s="36"/>
+    </row>
+    <row r="103" ht="14.25">
+      <c r="A103" s="24">
+        <v>102</v>
+      </c>
+      <c r="B103" s="24">
+        <v>12</v>
+      </c>
+      <c r="C103" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" ht="14.25">
+      <c r="A104" s="24">
+        <v>103</v>
+      </c>
+      <c r="B104" s="24">
+        <v>12</v>
+      </c>
+      <c r="C104" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D104" s="37"/>
+    </row>
+    <row r="105" ht="14.25">
+      <c r="A105" s="24">
+        <v>104</v>
+      </c>
+      <c r="B105" s="24">
+        <v>12</v>
+      </c>
+      <c r="C105" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D105" s="37"/>
+    </row>
+    <row r="106" ht="14.25">
+      <c r="A106" s="24">
+        <v>105</v>
+      </c>
+      <c r="B106" s="24">
+        <v>12</v>
+      </c>
+      <c r="C106" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D106" s="37"/>
+    </row>
+    <row r="107" ht="14.25">
+      <c r="A107" s="24">
+        <v>106</v>
+      </c>
+      <c r="B107" s="24">
+        <v>12</v>
+      </c>
+      <c r="C107" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D107" s="37"/>
+    </row>
+    <row r="108" ht="14.25">
+      <c r="A108" s="22">
+        <v>107</v>
+      </c>
+      <c r="B108" s="22">
+        <v>13</v>
+      </c>
+      <c r="C108" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" ht="14.25">
+      <c r="A109" s="24">
+        <v>108</v>
+      </c>
+      <c r="B109" s="24">
+        <v>14</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D109" s="37"/>
+    </row>
+    <row r="110" ht="14.25">
+      <c r="A110" s="22">
+        <v>109</v>
+      </c>
+      <c r="B110" s="22">
+        <v>15</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D110" s="40"/>
+    </row>
+    <row r="111" ht="14.25">
+      <c r="A111" s="24">
+        <v>110</v>
+      </c>
+      <c r="B111" s="24">
+        <v>16</v>
+      </c>
+      <c r="C111" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D111" s="41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" ht="14.25">
+      <c r="A112" s="24">
+        <v>111</v>
+      </c>
+      <c r="B112" s="24">
+        <v>16</v>
+      </c>
+      <c r="C112" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D112" s="41">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113" ht="14.25">
+      <c r="A113" s="24">
+        <v>112</v>
+      </c>
+      <c r="B113" s="24">
+        <v>16</v>
+      </c>
+      <c r="C113" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113" s="41"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D113"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>